--- a/data/trans_dic/P15B_tráfico-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15B_tráfico-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,62; 47,42</t>
+          <t>11,95; 48,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 36,66</t>
+          <t>14,77; 36,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 30,02</t>
+          <t>8,08; 29,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 42,17</t>
+          <t>13,93; 40,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 22,19</t>
+          <t>4,13; 22,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,52</t>
+          <t>5,51; 17,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 18,57</t>
+          <t>3,42; 17,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 14,95</t>
+          <t>5,62; 15,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 26,81</t>
+          <t>9,52; 27,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 22,12</t>
+          <t>10,6; 22,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 18,57</t>
+          <t>7,2; 19,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 19,89</t>
+          <t>9,57; 21,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,47; 45,38</t>
+          <t>24,32; 45,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,01; 33,19</t>
+          <t>20,29; 33,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 33,51</t>
+          <t>17,33; 33,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 35,24</t>
+          <t>16,7; 31,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 47,78</t>
+          <t>16,78; 49,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 33,92</t>
+          <t>16,94; 33,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 36,77</t>
+          <t>17,24; 36,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,61; 41,57</t>
+          <t>20,21; 40,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,79; 41,78</t>
+          <t>24,55; 43,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,44; 30,74</t>
+          <t>20,77; 30,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 31,78</t>
+          <t>19,5; 31,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,23; 34,89</t>
+          <t>20,47; 32,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 57,22</t>
+          <t>11,77; 62,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 42,17</t>
+          <t>10,02; 41,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 36,27</t>
+          <t>6,41; 37,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 63,04</t>
+          <t>22,2; 63,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 58,83</t>
+          <t>7,53; 57,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 52,39</t>
+          <t>15,71; 51,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 29,18</t>
+          <t>3,04; 29,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,82; 39,97</t>
+          <t>17,14; 42,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 49,38</t>
+          <t>15,36; 48,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 40,89</t>
+          <t>15,82; 41,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 26,12</t>
+          <t>7,09; 26,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 47,84</t>
+          <t>22,02; 48,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 42,65</t>
+          <t>23,93; 41,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,2; 30,72</t>
+          <t>20,16; 30,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 27,89</t>
+          <t>15,81; 28,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,62; 34,95</t>
+          <t>20,26; 34,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,73; 29,85</t>
+          <t>13,58; 30,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,24</t>
+          <t>13,89; 24,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,19</t>
+          <t>12,07; 23,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 28,99</t>
+          <t>16,35; 28,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 33,86</t>
+          <t>22,05; 34,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 25,86</t>
+          <t>18,86; 26,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 23,72</t>
+          <t>15,62; 23,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 29,72</t>
+          <t>20,26; 28,85</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>17638</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2926; 11939</t>
+          <t>3009; 12204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11531; 28130</t>
+          <t>11338; 28148</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3732; 13476</t>
+          <t>3628; 13178</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4288; 15014</t>
+          <t>5272; 15245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1937; 10103</t>
+          <t>1882; 10022</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6149; 18652</t>
+          <t>6227; 19761</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2711; 13855</t>
+          <t>2549; 13363</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4232; 11897</t>
+          <t>4748; 12886</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6178; 18958</t>
+          <t>6729; 19285</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21315; 41960</t>
+          <t>20110; 41843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7710; 22189</t>
+          <t>8600; 23322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10026; 22900</t>
+          <t>11705; 26251</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>32451</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>65682</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18423; 35622</t>
+          <t>19091; 35830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36670; 60827</t>
+          <t>37191; 62227</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19681; 40248</t>
+          <t>20813; 39848</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21592; 45496</t>
+          <t>23235; 44502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6120; 16742</t>
+          <t>5879; 17185</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19693; 38565</t>
+          <t>19262; 38446</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15187; 31569</t>
+          <t>14803; 30962</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21014; 42385</t>
+          <t>22440; 44988</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27013; 47443</t>
+          <t>27873; 48922</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60711; 91298</t>
+          <t>61695; 91979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39646; 65465</t>
+          <t>40171; 65275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49057; 80610</t>
+          <t>51195; 82396</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>26339</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2247; 11101</t>
+          <t>2283; 12057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2086; 10986</t>
+          <t>2610; 10731</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2019; 11170</t>
+          <t>1973; 11497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7230; 20945</t>
+          <t>9249; 26283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>918; 7787</t>
+          <t>996; 7580</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4375; 15074</t>
+          <t>4519; 14759</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>949; 9048</t>
+          <t>941; 9241</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4574; 12336</t>
+          <t>6041; 14907</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4503; 16117</t>
+          <t>5013; 15905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8947; 22418</t>
+          <t>8674; 22579</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3958; 16143</t>
+          <t>4380; 16179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13621; 30660</t>
+          <t>16935; 37271</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>50302</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99563</t>
+          <t>109658</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30076; 52497</t>
+          <t>29457; 50560</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57798; 87890</t>
+          <t>57681; 88282</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31826; 54608</t>
+          <t>30957; 55293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38843; 69176</t>
+          <t>44298; 75165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12875; 28002</t>
+          <t>12735; 28731</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35916; 61910</t>
+          <t>35480; 61417</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23578; 44404</t>
+          <t>23115; 44219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36254; 61561</t>
+          <t>37739; 64897</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46470; 73427</t>
+          <t>47830; 75745</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100824; 140036</t>
+          <t>102105; 142249</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59832; 91877</t>
+          <t>60472; 91959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82063; 121932</t>
+          <t>91039; 129652</t>
         </is>
       </c>
     </row>
